--- a/artfynd/A 60594-2024 artfynd.xlsx
+++ b/artfynd/A 60594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123420677</v>
       </c>
       <c r="B2" t="n">
-        <v>58313</v>
+        <v>58319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60594-2024 artfynd.xlsx
+++ b/artfynd/A 60594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123420677</v>
       </c>
       <c r="B2" t="n">
-        <v>58319</v>
+        <v>58322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60594-2024 artfynd.xlsx
+++ b/artfynd/A 60594-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123420677</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60594-2024 artfynd.xlsx
+++ b/artfynd/A 60594-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420677</v>
+        <v>123420675</v>
       </c>
       <c r="B2" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>101268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Margaritifera margaritifera</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtossena, Hls</t>
+          <t>Pockeboån, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599569</v>
+        <v>599644</v>
       </c>
       <c r="R2" t="n">
-        <v>6828768</v>
+        <v>6828766</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2432</t>
+          <t>2024_2434</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>förekommer spritt längsmed pockeboån</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,6 +798,396 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123420676</v>
+      </c>
+      <c r="B3" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pockeboån, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>599604</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6828773</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Njutånger</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_2433</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>förekommer spritt längsmed pockeboån</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123420680</v>
+      </c>
+      <c r="B4" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pockeboån, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>599513</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6828773</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_2429</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>förekommer spritt längsmed hela pockeboån</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123420677</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtossena, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>599569</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6828768</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njutånger</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_2432</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>juvenil</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
